--- a/4. Supervised Learning (modeling and evaluation)/weights_layer3.xlsx
+++ b/4. Supervised Learning (modeling and evaluation)/weights_layer3.xlsx
@@ -441,1102 +441,1102 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0.02811170763267307</v>
+        <v>0.04058397449964894</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.07826125238725755</v>
+        <v>0.03178960630189957</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05198639412035283</v>
+        <v>-0.1077400947566013</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-2.351635644831681e-08</v>
+        <v>0.01514030228434155</v>
       </c>
       <c r="B3" t="n">
-        <v>-5.580417678848953e-08</v>
+        <v>0.03691610357026984</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04645806377777716</v>
+        <v>-0.01571147216505946</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0.09835942099761995</v>
+        <v>-0.1290227938269627</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.1756713247155781</v>
+        <v>-0.03734567774758042</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.0604118366227008</v>
+        <v>-0.1117931770244212</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0.1162188321043618</v>
+        <v>0.129802376945643</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.1669275378842655</v>
+        <v>0.09310434192070513</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1464219374597453</v>
+        <v>-0.1155291296981102</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0.007985147590942421</v>
+        <v>-0.0280531237909482</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.02202254437225137</v>
+        <v>2.011228043483123e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.05052687935647131</v>
+        <v>1.8902015193269e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0.02622565524420811</v>
+        <v>0.03010524310699895</v>
       </c>
       <c r="B7" t="n">
-        <v>-2.638859710766826e-06</v>
+        <v>-2.41838873311129e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02156842937242058</v>
+        <v>0.00236427797347231</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.1111593222106727</v>
+        <v>-0.04520777069733681</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.09385422311150657</v>
+        <v>0.1047363550611471</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05136298369211158</v>
+        <v>-0.03018307294999207</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.06217547433458897</v>
+        <v>-1.691284567422935e-06</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.2040283527519572</v>
+        <v>0.0002613127976798534</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.2399863270597492</v>
+        <v>0.090370073125593</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0.150073250823658</v>
+        <v>-0.1913089233825004</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1670624492661224</v>
+        <v>-0.0851814987583631</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.2498371677575917</v>
+        <v>0.008627611266535341</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.01114230966716615</v>
+        <v>-0.0005889280941085618</v>
       </c>
       <c r="B11" t="n">
-        <v>0.142277125699511</v>
+        <v>-0.007920683901163027</v>
       </c>
       <c r="C11" t="n">
-        <v>0.07370383671047322</v>
+        <v>1.887523684355702e-06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-0.03332463210036424</v>
+        <v>0.05942225999990083</v>
       </c>
       <c r="B12" t="n">
-        <v>5.135361225006295e-05</v>
+        <v>-0.02345236484677762</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.05743983263167129</v>
+        <v>-0.1178401635470438</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-0.184939035514346</v>
+        <v>-0.08442024917239285</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.3597277495546455</v>
+        <v>-0.0198193682527824</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2513969532367255</v>
+        <v>0.04651415599592241</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.02746488684596669</v>
+        <v>0.2055210083665743</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1367153419383917</v>
+        <v>0.04266223568950608</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2194325425664371</v>
+        <v>-0.1578255438196109</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0.230070913341288</v>
+        <v>0.01831757213684897</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.05260964747362033</v>
+        <v>-0.176580628978627</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.153372621983138</v>
+        <v>-0.2036399510772244</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.1670585726962796</v>
+        <v>-0.07933976688586347</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.01301063160472955</v>
+        <v>0.06895070125685658</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2126489633285145</v>
+        <v>0.04050914775936209</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.06727219075566575</v>
+        <v>-0.09191266741013429</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.1358007263614504</v>
+        <v>0.09133581563806986</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.1150139003168238</v>
+        <v>0.002664726602695098</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.1444176934605021</v>
+        <v>-0.1075470397808142</v>
       </c>
       <c r="B18" t="n">
-        <v>0.09809563050557492</v>
+        <v>-0.0009683418979300311</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1631517206511029</v>
+        <v>-0.0457023054176751</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2.433268121583628e-06</v>
+        <v>-0.03150171906255301</v>
       </c>
       <c r="B19" t="n">
-        <v>0.01915496154477709</v>
+        <v>0.06977534266192426</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0184746680931984</v>
+        <v>0.1635188005562534</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-0.1297139934795568</v>
+        <v>0.03389772367149761</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.006581600164854269</v>
+        <v>0.0279960223107373</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.02681981709525279</v>
+        <v>-2.771558175754924e-05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-0.1018300870341078</v>
+        <v>0.09962399610358803</v>
       </c>
       <c r="B21" t="n">
-        <v>0.03201903619142314</v>
+        <v>0.003734281752448182</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1771353674078319</v>
+        <v>-0.03696783906177555</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.02495475569670309</v>
+        <v>-0.1846078706903223</v>
       </c>
       <c r="B22" t="n">
-        <v>0.001069211243497564</v>
+        <v>-0.225067253454593</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1976712099183681</v>
+        <v>0.1661244695085176</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-0.08454767800329951</v>
+        <v>-0.1262590078672598</v>
       </c>
       <c r="B23" t="n">
-        <v>0.009261340633696146</v>
+        <v>0.1950843418340168</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.2007553378575565</v>
+        <v>0.02179749904482776</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-0.2236005624988906</v>
+        <v>0.1409440659634928</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0347044103747547</v>
+        <v>0.1102339844260598</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.15124669083574</v>
+        <v>-0.02719710746929243</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.05534744419660077</v>
+        <v>0.07646635527251831</v>
       </c>
       <c r="B25" t="n">
-        <v>1.371190116694711e-07</v>
+        <v>-0.09272077092975428</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.05630421890974836</v>
+        <v>2.073066986911239e-06</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-0.02232069542584244</v>
+        <v>-0.1295866090113327</v>
       </c>
       <c r="B26" t="n">
-        <v>0.1677790289519149</v>
+        <v>0.2214478981515293</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2429375122688997</v>
+        <v>0.09423461435263918</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-0.02644507502498324</v>
+        <v>-0.06646283433254431</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.03933668736768651</v>
+        <v>0.2346327279803093</v>
       </c>
       <c r="C27" t="n">
-        <v>0.01809693957605862</v>
+        <v>0.1283952879295935</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-0.1653090097022141</v>
+        <v>-0.2309040686366727</v>
       </c>
       <c r="B28" t="n">
-        <v>0.1371997452589426</v>
+        <v>-0.09453434527004062</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1131119791557709</v>
+        <v>0.02676428319867597</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.09540903769741085</v>
+        <v>-0.2193460755108809</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.04025955595969373</v>
+        <v>-0.1862409441422328</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1534245520404338</v>
+        <v>0.1103470034371082</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.01343433655354511</v>
+        <v>-0.07488138888982168</v>
       </c>
       <c r="B30" t="n">
-        <v>0.06127924413850545</v>
+        <v>-0.06040863152814013</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1828173654419744</v>
+        <v>0.01667963277349874</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-0.07736052572419995</v>
+        <v>-0.1672833152903566</v>
       </c>
       <c r="B31" t="n">
-        <v>0.06044954518113742</v>
+        <v>0.001721458869908019</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1111022697128011</v>
+        <v>0.02370254661573783</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-0.08109776397736838</v>
+        <v>0.003228093714187892</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1423040419535966</v>
+        <v>-0.001092320394833808</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0331573778442236</v>
+        <v>8.690362388891214e-05</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.2464621394564514</v>
+        <v>0.0162716129925709</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.1474949700193148</v>
+        <v>-0.08190429999794437</v>
       </c>
       <c r="C33" t="n">
-        <v>0.07704179496977574</v>
+        <v>0.06251303501733807</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.1437726344261472</v>
+        <v>-0.01425641276449574</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.02006536088860454</v>
+        <v>0.06076494485003254</v>
       </c>
       <c r="C34" t="n">
-        <v>0.116404305172908</v>
+        <v>0.1930039940483468</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-0.1482515772353417</v>
+        <v>0.0007279108677087362</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.06632844140763883</v>
+        <v>0.007906101843191748</v>
       </c>
       <c r="C35" t="n">
-        <v>0.002702450634627488</v>
+        <v>0.05261325837733539</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.1782278246153031</v>
+        <v>0.2587837861587347</v>
       </c>
       <c r="B36" t="n">
-        <v>0.214261434262926</v>
+        <v>-0.2277224299985482</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1214422651403222</v>
+        <v>0.1220924390670057</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.03909423478775289</v>
+        <v>-0.09150482218891956</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.1826947686962</v>
+        <v>-0.02186419406487644</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1798159953609385</v>
+        <v>-0.2404783851915835</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.19130756565263</v>
+        <v>0.02158756863488022</v>
       </c>
       <c r="B38" t="n">
-        <v>0.1634530502804169</v>
+        <v>-0.1855641280602624</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1808484045415909</v>
+        <v>-0.1542450775802015</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>-0.2498676893524058</v>
+        <v>0.1061274224169861</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.1794217696016732</v>
+        <v>-0.01568902711923428</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.004852054004854627</v>
+        <v>-0.0699051895012987</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.03780207390922723</v>
+        <v>0.2274296710515422</v>
       </c>
       <c r="B40" t="n">
-        <v>0.03750038898988391</v>
+        <v>0.1120642523312749</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1331196742375135</v>
+        <v>0.07343227049699047</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.02999669380106324</v>
+        <v>-0.1246008200728252</v>
       </c>
       <c r="B41" t="n">
-        <v>-1.1594544037359e-09</v>
+        <v>-0.1563241227266486</v>
       </c>
       <c r="C41" t="n">
-        <v>0.04634426236516492</v>
+        <v>0.0267584665694544</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.09347025384523854</v>
+        <v>-0.2004984161901625</v>
       </c>
       <c r="B42" t="n">
-        <v>0.1272766601555258</v>
+        <v>0.2236687393150585</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2193903417914745</v>
+        <v>-0.002780090728440651</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>-0.07824503407069885</v>
+        <v>0.1197503949903745</v>
       </c>
       <c r="B43" t="n">
-        <v>-0.04497751584911249</v>
+        <v>-0.08485490972147502</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.003269877877377467</v>
+        <v>-0.1515574117743451</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>-0.2525159934816192</v>
+        <v>-0.02664728003344743</v>
       </c>
       <c r="B44" t="n">
-        <v>0.07603233417216856</v>
+        <v>-0.2518779013565648</v>
       </c>
       <c r="C44" t="n">
-        <v>0.09453446014523587</v>
+        <v>-0.1221834442292371</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>-0.0373427443537987</v>
+        <v>-0.04896779086386515</v>
       </c>
       <c r="B45" t="n">
-        <v>-0.09003612014297076</v>
+        <v>-0.2410233324430124</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.1752153938858488</v>
+        <v>-0.04924262893633526</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.1414581545020644</v>
+        <v>-0.02870613036301212</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.08062369756897879</v>
+        <v>0.007603226256425726</v>
       </c>
       <c r="C46" t="n">
-        <v>0.07863998692124557</v>
+        <v>-0.01011103966453168</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>-0.1647816533366324</v>
+        <v>-0.1363897818761447</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.1281066816878335</v>
+        <v>0.09558262132504197</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.04352154284538177</v>
+        <v>0.1472800489405229</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>-2.896781157262524e-05</v>
+        <v>0.08255402508833851</v>
       </c>
       <c r="B48" t="n">
-        <v>-1.737413104850103e-07</v>
+        <v>-0.2196274576507585</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0148152751217871</v>
+        <v>0.208439134536137</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>-0.07444459176383582</v>
+        <v>-0.2253293633598758</v>
       </c>
       <c r="B49" t="n">
-        <v>-0.08543090020075161</v>
+        <v>-0.03196156541137481</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.2464363991981848</v>
+        <v>0.09153540841294149</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-0.03327703060193103</v>
+        <v>-0.1775807479548148</v>
       </c>
       <c r="B50" t="n">
-        <v>-0.2322744796323765</v>
+        <v>-0.1537704357785246</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0794409235366499</v>
+        <v>-0.2107767279018392</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.01143651251512459</v>
+        <v>0.05018549371628642</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.1753717811683722</v>
+        <v>-0.05123153537605761</v>
       </c>
       <c r="C51" t="n">
-        <v>0.06293879851798691</v>
+        <v>0.2191161713540214</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>-1.704705079973377e-08</v>
+        <v>0.2201214378591941</v>
       </c>
       <c r="B52" t="n">
-        <v>8.888477803909276e-10</v>
+        <v>0.2151748969613637</v>
       </c>
       <c r="C52" t="n">
-        <v>0.02605430087038541</v>
+        <v>-0.09740360483701714</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>-0.1056364754241127</v>
+        <v>-0.07154671139716037</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.1611859600018376</v>
+        <v>0.07177221108676744</v>
       </c>
       <c r="C53" t="n">
-        <v>0.125959238294419</v>
+        <v>1.045176013907729e-06</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.2543333667390671</v>
+        <v>-0.03433205478520059</v>
       </c>
       <c r="B54" t="n">
-        <v>-0.07365354651433273</v>
+        <v>0.03255112865768084</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1532546280673723</v>
+        <v>0.1818671189847793</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.178680625989139</v>
+        <v>-0.08836171066561385</v>
       </c>
       <c r="B55" t="n">
-        <v>-0.03909358510397919</v>
+        <v>-3.276956076531414e-06</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1486387428235988</v>
+        <v>-0.002712329292882261</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.2117651347204239</v>
+        <v>0.1966042338497954</v>
       </c>
       <c r="B56" t="n">
-        <v>-0.09023603367284826</v>
+        <v>-0.08281895655741857</v>
       </c>
       <c r="C56" t="n">
-        <v>0.1263001762128948</v>
+        <v>0.09903572981607194</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>-0.00137706508101583</v>
+        <v>0.1549450470536097</v>
       </c>
       <c r="B57" t="n">
-        <v>-0.003773213360428377</v>
+        <v>0.1909980921103906</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.01114491837209789</v>
+        <v>-0.1574270683426059</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>-0.2399951944676304</v>
+        <v>-0.01205652806508664</v>
       </c>
       <c r="B58" t="n">
-        <v>0.1978341071181848</v>
+        <v>-0.001976984952305603</v>
       </c>
       <c r="C58" t="n">
-        <v>0.02291656674429866</v>
+        <v>-1.971162055343504e-06</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>-0.2123611504606755</v>
+        <v>-0.0886993815378098</v>
       </c>
       <c r="B59" t="n">
-        <v>-0.0712575737633207</v>
+        <v>-0.04377338397243609</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.004367232632328845</v>
+        <v>-0.1450824915188182</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>-0.1386002446616662</v>
+        <v>-0.06099576644328652</v>
       </c>
       <c r="B60" t="n">
-        <v>0.03789174767469971</v>
+        <v>-0.01904649743089211</v>
       </c>
       <c r="C60" t="n">
-        <v>0.1559318659670617</v>
+        <v>0.2042205759893686</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>-0.1823345464880695</v>
+        <v>0.033471984856657</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.1734852305824533</v>
+        <v>-0.005763108326896403</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.07428295342355531</v>
+        <v>0.1249073961683961</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.2069882897794769</v>
+        <v>-0.228772932480947</v>
       </c>
       <c r="B62" t="n">
-        <v>0.2190178559934546</v>
+        <v>0.1661532937445265</v>
       </c>
       <c r="C62" t="n">
-        <v>0.05877563387834943</v>
+        <v>0.1289703552382411</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.1436703239567055</v>
+        <v>0.1874328491097712</v>
       </c>
       <c r="B63" t="n">
-        <v>0.1462749961431624</v>
+        <v>-0.2076675663488099</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1721449395452898</v>
+        <v>0.111354354664417</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.2107196549661643</v>
+        <v>0.09806668467368641</v>
       </c>
       <c r="B64" t="n">
-        <v>0.1780321516872453</v>
+        <v>-0.003549796793008958</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.05525374787008007</v>
+        <v>-0.1099192729276832</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.1041054684442192</v>
+        <v>0.2386355524258129</v>
       </c>
       <c r="B65" t="n">
-        <v>-0.06666534052170392</v>
+        <v>0.05081560926557499</v>
       </c>
       <c r="C65" t="n">
-        <v>0.168275532405847</v>
+        <v>0.1708587102989274</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.06133224661380638</v>
+        <v>0.1814825895015408</v>
       </c>
       <c r="B66" t="n">
-        <v>-0.1638448692772425</v>
+        <v>0.0273776219576297</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.1600366505323745</v>
+        <v>0.2293128393992716</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.1014552775685852</v>
+        <v>0.2012246261201058</v>
       </c>
       <c r="B67" t="n">
-        <v>0.1830613634659801</v>
+        <v>-0.1851963023040048</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.02248472355826482</v>
+        <v>0.1814585701782953</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>-0.01501386442599697</v>
+        <v>-0.08259542156951456</v>
       </c>
       <c r="B68" t="n">
-        <v>-0.0007264523685968731</v>
+        <v>0.168297341162917</v>
       </c>
       <c r="C68" t="n">
-        <v>-3.715006087278302e-05</v>
+        <v>-0.1644178471355094</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>-0.01912090275948138</v>
+        <v>0.250302380582572</v>
       </c>
       <c r="B69" t="n">
-        <v>-0.0003563803655802619</v>
+        <v>-0.2239058131986217</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.05009414771137968</v>
+        <v>0.03078122158118167</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>-0.1757530691078207</v>
+        <v>-0.07719229438067667</v>
       </c>
       <c r="B70" t="n">
-        <v>0.1138720202071363</v>
+        <v>0.03735806491267155</v>
       </c>
       <c r="C70" t="n">
-        <v>0.06143317566155349</v>
+        <v>-0.2191479601514979</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>-0.04029633123615037</v>
+        <v>0.1273109131649218</v>
       </c>
       <c r="B71" t="n">
-        <v>0.1590304668206844</v>
+        <v>0.06167915812112299</v>
       </c>
       <c r="C71" t="n">
-        <v>0.0814989269762926</v>
+        <v>-0.1536901911298156</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.0007415806473831171</v>
+        <v>-0.05632656411252257</v>
       </c>
       <c r="B72" t="n">
-        <v>-0.04117600120360418</v>
+        <v>-0.1868712068469375</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.02047941011406672</v>
+        <v>0.07552564377626336</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.04471256785783986</v>
+        <v>0.2244048264462156</v>
       </c>
       <c r="B73" t="n">
-        <v>0.002357836901957493</v>
+        <v>0.1868277295349506</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.1787760255425507</v>
+        <v>-0.01673531204528781</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-1.386061911342103e-05</v>
+        <v>-3.63535706286332e-06</v>
       </c>
       <c r="B74" t="n">
-        <v>-0.01365500066859152</v>
+        <v>-0.002697104628623112</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0424594773993556</v>
+        <v>-0.1025938880093793</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.1331852315138178</v>
+        <v>-0.1978930591046434</v>
       </c>
       <c r="B75" t="n">
-        <v>-0.001527382643684396</v>
+        <v>0.13137920079796</v>
       </c>
       <c r="C75" t="n">
-        <v>0.06859092412655034</v>
+        <v>-0.234495757057472</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.01924911162023507</v>
+        <v>-0.05040096105551491</v>
       </c>
       <c r="B76" t="n">
-        <v>-0.02840006878469975</v>
+        <v>-0.1839752137412755</v>
       </c>
       <c r="C76" t="n">
-        <v>-7.311149674620883e-10</v>
+        <v>-0.1509905231404202</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>-0.1674887196869302</v>
+        <v>0.09629720448146428</v>
       </c>
       <c r="B77" t="n">
-        <v>-0.01006266004075183</v>
+        <v>-0.07088444620009812</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.1107900539586314</v>
+        <v>0.2345665231739253</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.1420222650924439</v>
+        <v>0.2374763004155781</v>
       </c>
       <c r="B78" t="n">
-        <v>0.1015274265602062</v>
+        <v>-0.2114011428363209</v>
       </c>
       <c r="C78" t="n">
-        <v>0.02969799197398374</v>
+        <v>-0.1182995141305715</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0.222249063507189</v>
+        <v>-0.182313634324091</v>
       </c>
       <c r="B79" t="n">
-        <v>-0.1790754580419825</v>
+        <v>0.003388556196575182</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.1191638075155358</v>
+        <v>-0.1445759841862792</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.1450939597776995</v>
+        <v>-0.06341026779191254</v>
       </c>
       <c r="B80" t="n">
-        <v>-0.210150302796075</v>
+        <v>0.04615229063560733</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1665835839358051</v>
+        <v>0.02564207252525355</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0.196141250583483</v>
+        <v>-0.1597106364579007</v>
       </c>
       <c r="B81" t="n">
-        <v>-0.1506108080576205</v>
+        <v>-0.08705688710587539</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.07004204443487949</v>
+        <v>0.1096991996817256</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>0.1228592326690544</v>
+        <v>0.1656769265283069</v>
       </c>
       <c r="B82" t="n">
-        <v>-0.05857904246999839</v>
+        <v>0.2011242271788893</v>
       </c>
       <c r="C82" t="n">
-        <v>0.03219603745436506</v>
+        <v>0.1504581101807725</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0.004396281280908276</v>
+        <v>0.2346117897574263</v>
       </c>
       <c r="B83" t="n">
-        <v>0.1573652242321727</v>
+        <v>-0.2015975703314675</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.1738586476845775</v>
+        <v>-0.00207083648193403</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0.01362564367071382</v>
+        <v>0.004822148522064965</v>
       </c>
       <c r="B84" t="n">
-        <v>-0.06707619723533374</v>
+        <v>0.2099817211173623</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.03712558281879403</v>
+        <v>-0.07938314144367258</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>-0.1551467266743162</v>
+        <v>-0.09620067905370615</v>
       </c>
       <c r="B85" t="n">
-        <v>0.08598538117786891</v>
+        <v>0.1153377744527811</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.05262547186344953</v>
+        <v>-0.07109156075416855</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>-0.1053896533648576</v>
+        <v>-0.1346091530287983</v>
       </c>
       <c r="B86" t="n">
-        <v>0.04881100171900851</v>
+        <v>-0.0002913459641961208</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1302590214739902</v>
+        <v>-0.1117581691197209</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>0.0532554592952522</v>
+        <v>-0.1033095723612748</v>
       </c>
       <c r="B87" t="n">
-        <v>0.04239089460352406</v>
+        <v>-4.983972282110135e-05</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.05532832611616927</v>
+        <v>-0.06433219747885885</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>0.02295893800377187</v>
+        <v>0.120660451082759</v>
       </c>
       <c r="B88" t="n">
-        <v>-0.1378471034943402</v>
+        <v>-0.02161329804823623</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.2429496332990593</v>
+        <v>0.1656094378832291</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>-0.004235859189085624</v>
+        <v>0.2259312172750276</v>
       </c>
       <c r="B89" t="n">
-        <v>-0.02380607329765884</v>
+        <v>0.08368445183988514</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.003102904503249081</v>
+        <v>-0.2380221391106891</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>0.09640689424635844</v>
+        <v>0.07993506531456021</v>
       </c>
       <c r="B90" t="n">
-        <v>-0.2066817114013982</v>
+        <v>0.04232075149206118</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.019299407929507</v>
+        <v>0.1972578148254625</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>0.05699211203410957</v>
+        <v>0.02635013299008999</v>
       </c>
       <c r="B91" t="n">
-        <v>-0.05405441872988088</v>
+        <v>1.458909236951418e-06</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.1112080691700598</v>
+        <v>0.08348719639011676</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.001193448878790984</v>
+        <v>0.01980766315071286</v>
       </c>
       <c r="B92" t="n">
-        <v>0.0001991106220996808</v>
+        <v>0.2091165832111628</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.05017543151465655</v>
+        <v>0.07343246078654495</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>0.2105221173875327</v>
+        <v>-0.01218252546858296</v>
       </c>
       <c r="B93" t="n">
-        <v>-0.1154957193864896</v>
+        <v>0.2307396321203217</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.1647573466428967</v>
+        <v>-0.2163858858647644</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0.1502425331045847</v>
+        <v>0.02373911662936292</v>
       </c>
       <c r="B94" t="n">
-        <v>0.05962713129535158</v>
+        <v>0.1050058528971889</v>
       </c>
       <c r="C94" t="n">
-        <v>0.1168276846681174</v>
+        <v>-0.002605618666749959</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>0.1334529362565757</v>
+        <v>-0.01368277210745841</v>
       </c>
       <c r="B95" t="n">
-        <v>-0.1082054256924771</v>
+        <v>0.00473004537970347</v>
       </c>
       <c r="C95" t="n">
-        <v>0.2206541846540901</v>
+        <v>-0.1046073685904289</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>-0.01716048604977593</v>
+        <v>-0.1912240410898596</v>
       </c>
       <c r="B96" t="n">
-        <v>0.07240782950387413</v>
+        <v>0.1275004780607362</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.07784854623919671</v>
+        <v>0.0663748240834062</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-0.06869136062221061</v>
+        <v>-0.03435849302436053</v>
       </c>
       <c r="B97" t="n">
-        <v>-0.1734757039873694</v>
+        <v>-0.1451200578583018</v>
       </c>
       <c r="C97" t="n">
-        <v>0.1108843289799769</v>
+        <v>0.08717426126350983</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>0.1384187753934788</v>
+        <v>-0.1206827437521646</v>
       </c>
       <c r="B98" t="n">
-        <v>-0.05221164305029353</v>
+        <v>0.0450951539994901</v>
       </c>
       <c r="C98" t="n">
-        <v>0.002597374859701565</v>
+        <v>-0.04131708897831148</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>-0.001074285680928557</v>
+        <v>0.04839165948667021</v>
       </c>
       <c r="B99" t="n">
-        <v>0.1860820492367015</v>
+        <v>-0.002810069025118097</v>
       </c>
       <c r="C99" t="n">
-        <v>0.1325712353597087</v>
+        <v>0.000142971961050932</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>-0.169450675218787</v>
+        <v>0.1862977987665507</v>
       </c>
       <c r="B100" t="n">
-        <v>-0.07349396851639595</v>
+        <v>-0.2131348913609118</v>
       </c>
       <c r="C100" t="n">
-        <v>0.02584251708890642</v>
+        <v>-0.1641541505247673</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>-0.08535166223663999</v>
+        <v>-0.09393889031124658</v>
       </c>
       <c r="B101" t="n">
-        <v>0.003121104550445295</v>
+        <v>-0.03772666097046221</v>
       </c>
       <c r="C101" t="n">
-        <v>0.03907044973735673</v>
+        <v>-0.1756280007268147</v>
       </c>
     </row>
   </sheetData>
